--- a/data/trans_bre/IP41-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP41-Habitat-trans_bre.xlsx
@@ -660,17 +660,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 4,65</t>
+          <t>-3,49; 4,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 9,83</t>
+          <t>-2,64; 9,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,7; -1,38</t>
+          <t>-13,99; -1,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -680,17 +680,17 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 5,03</t>
+          <t>-3,6; 5,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 11,71</t>
+          <t>-2,83; 10,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-15,56; -1,67</t>
+          <t>-14,93; -1,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,17 +760,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,46; 1,48</t>
+          <t>-6,69; 1,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,81; 2,16</t>
+          <t>-7,04; 1,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 7,44</t>
+          <t>-4,67; 6,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -780,17 +780,17 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 1,61</t>
+          <t>-6,98; 1,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-7,31; 2,41</t>
+          <t>-7,5; 2,17</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 9,24</t>
+          <t>-5,35; 7,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -860,17 +860,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 4,15</t>
+          <t>-5,98; 4,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 7,67</t>
+          <t>-3,54; 7,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 12,98</t>
+          <t>-1,72; 12,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -880,17 +880,17 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 4,58</t>
+          <t>-6,26; 4,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 8,96</t>
+          <t>-3,95; 8,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 17,62</t>
+          <t>-2,05; 16,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -960,17 +960,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 3,5</t>
+          <t>-6,97; 3,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 7,54</t>
+          <t>-3,55; 7,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 7,93</t>
+          <t>-4,86; 7,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 4,09</t>
+          <t>-7,71; 4,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 9,22</t>
+          <t>-4,09; 9,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 10,26</t>
+          <t>-5,92; 10,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 0,97</t>
+          <t>-3,64; 0,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 3,82</t>
+          <t>-1,75; 3,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 3,35</t>
+          <t>-2,79; 3,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1080,17 +1080,17 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 1,06</t>
+          <t>-3,91; 1,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 4,4</t>
+          <t>-1,98; 4,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 4,0</t>
+          <t>-3,27; 4,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">

--- a/data/trans_bre/IP41-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP41-Habitat-trans_bre.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -515,8 +515,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -533,15 +531,13 @@
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Brecha de género relativa</t>
         </is>
       </c>
+      <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="n"/>
-      <c r="J1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -563,27 +559,17 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
           <t>2016</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
         </is>
       </c>
     </row>
@@ -596,8 +582,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -627,27 +611,17 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
           <t>-8,45%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -660,42 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 4,99</t>
+          <t>-3,25; 4,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 9,18</t>
+          <t>-1,57; 9,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,99; -1,29</t>
+          <t>-14,07; -1,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,37; 5,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 5,34</t>
+          <t>-1,62; 11,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 10,94</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-14,93; -1,47</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-14,92; -1,47</t>
         </is>
       </c>
     </row>
@@ -727,27 +691,17 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-2,66%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>-2,66%</t>
+          <t>-2,72%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-2,72%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
           <t>1,57%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -760,42 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 1,24</t>
+          <t>-6,23; 1,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 1,97</t>
+          <t>-7,13; 1,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 6,45</t>
+          <t>-3,85; 6,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-6,53; 1,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 1,33</t>
+          <t>-7,59; 1,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 2,17</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-5,35; 7,84</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-4,46; 8,16</t>
         </is>
       </c>
     </row>
@@ -827,27 +771,17 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-0,68%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>-0,68%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
           <t>7,09%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -860,42 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 4,28</t>
+          <t>-5,56; 4,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 7,49</t>
+          <t>-3,08; 7,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 12,24</t>
+          <t>-0,89; 12,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-5,93; 4,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 4,82</t>
+          <t>-3,37; 8,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 8,88</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-2,05; 16,75</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-1,07; 16,84</t>
         </is>
       </c>
     </row>
@@ -927,27 +851,17 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-1,72%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>-1,72%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
           <t>1,71%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -960,42 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 3,84</t>
+          <t>-6,99; 4,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 7,89</t>
+          <t>-3,93; 7,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 7,84</t>
+          <t>-4,98; 7,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-7,72; 4,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 4,45</t>
+          <t>-4,37; 9,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 9,67</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-5,92; 10,15</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-6,04; 10,18</t>
         </is>
       </c>
     </row>
@@ -1027,27 +931,17 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-1,4%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>-1,4%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
           <t>0,52%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 0,99</t>
+          <t>-3,82; 1,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 3,55</t>
+          <t>-1,75; 3,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 3,94</t>
+          <t>-2,75; 3,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,11; 1,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 1,07</t>
+          <t>-1,92; 4,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 4,08</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-3,27; 4,83</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-3,22; 4,73</t>
         </is>
       </c>
     </row>
@@ -1108,12 +992,12 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
+    <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A10:A11"/>
   </mergeCells>

--- a/data/trans_bre/IP41-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP41-Habitat-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 4,68</t>
+          <t>-3,84; 4,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 9,54</t>
+          <t>-2,25; 9,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,07; -1,38</t>
+          <t>-14,7; -1,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 5,09</t>
+          <t>-4,03; 5,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 11,52</t>
+          <t>-2,45; 11,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-14,92; -1,47</t>
+          <t>-15,56; -1,67</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 1,34</t>
+          <t>-6,46; 1,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 1,74</t>
+          <t>-6,81; 2,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 6,73</t>
+          <t>-4,0; 7,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 1,4</t>
+          <t>-6,73; 1,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-7,59; 1,94</t>
+          <t>-7,31; 2,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 8,16</t>
+          <t>-4,65; 9,24</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 4,13</t>
+          <t>-5,85; 4,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 7,42</t>
+          <t>-3,69; 7,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 12,52</t>
+          <t>-1,06; 12,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 4,58</t>
+          <t>-6,17; 4,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 8,84</t>
+          <t>-4,15; 8,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 16,84</t>
+          <t>-1,24; 17,62</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 4,01</t>
+          <t>-7,39; 3,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 7,57</t>
+          <t>-3,98; 7,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 7,9</t>
+          <t>-4,63; 7,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,72; 4,61</t>
+          <t>-8,15; 4,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 9,3</t>
+          <t>-4,53; 9,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 10,18</t>
+          <t>-5,61; 10,26</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 1,04</t>
+          <t>-3,81; 0,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 3,58</t>
+          <t>-1,89; 3,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 3,89</t>
+          <t>-2,81; 3,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 1,13</t>
+          <t>-4,06; 1,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 4,14</t>
+          <t>-2,11; 4,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 4,73</t>
+          <t>-3,31; 4,0</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP41-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP41-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,239 +603,163 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,66</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3,76</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-7,78</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4,26%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-8,45%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>0.6626775081895575</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>3.760200339063224</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-7.780598252723747</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>0.007009494806144437</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.04263191681134097</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.08454699992593559</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-3,84; 4,65</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-2,25; 9,83</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-14,7; -1,38</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-4,03; 5,03</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-2,45; 11,71</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-15,56; -1,67</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-3.843765993087397</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-2.24652402955771</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-14.69839571949894</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>-0.04028198619624145</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.02446805161359211</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.1555788026159303</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>4.646434320585353</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>9.833538484513854</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>-1.382234612478055</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>0.05032209456588971</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.1170726273369938</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>-0.01672040329358249</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-2,51</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-2,5</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,33</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-2,66%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-2,72%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-6,46; 1,48</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-6,81; 2,16</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-4,0; 7,44</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-6,73; 1,61</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-7,31; 2,41</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-4,65; 9,24</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-2.511684834983974</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-2.499476958634339</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1.326986785899087</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.02659140343284164</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.02720417681100423</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.01572262016093155</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-0,63</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1,95</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>5,57</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,68%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>7,09%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-6.457825804645621</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-6.80876437075792</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-3.998210621317467</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.06725464743880921</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.07310213380143042</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.04652266800924659</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-5,85; 4,15</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-3,69; 7,67</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-1,06; 12,98</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-6,17; 4,58</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-4,15; 8,96</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-1,24; 17,62</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1.483610116562674</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>2.160113381971108</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>7.435274273547359</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0.01613904969995673</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.0240507881587441</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.09242914835850062</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,157 +767,243 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-1,52</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1,83</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,39</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-1,72%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,16%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-0.6315669728005679</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1.946520252316997</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>5.570091267935606</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>-0.006822467261900673</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.02214572503722271</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.07093921680079313</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-7,39; 3,5</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-3,98; 7,54</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-4,63; 7,93</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-8,15; 4,09</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-4,53; 9,22</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-5,61; 10,26</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-5.853291240883301</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-3.693803592894284</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-1.058611308425745</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>-0.06171596115939667</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.04150665032563643</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.01236570523000504</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>4.145965214737394</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>7.6692213740532</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>12.97984946364694</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>0.0457717218615712</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.08961272076392506</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.1761943112704783</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-1.518186447328262</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>1.830610648021935</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>1.390619274986782</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.01715052601971599</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.02158804203194778</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.01710301401408427</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-7.392238716892032</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-3.976538686171919</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-4.630335570142459</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.08146401147056397</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.0452651897073592</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.0560813210578749</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>3.502706810631628</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>7.535963616540372</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>7.931515411063097</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.04090439566350444</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.09215812670157242</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.1026425764098024</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-1,29</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,89</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,44</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-1,4%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-3,81; 0,97</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-1,89; 3,82</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-2,81; 3,35</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-4,06; 1,06</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-2,11; 4,4</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-3,31; 4,0</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-1.291350389372303</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.887488743761522</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.438067261686359</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>-0.01397804185036947</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.01005256970818911</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.005230318811633617</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-3.807112858259318</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-1.890082802216952</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-2.810084340435331</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>-0.04060615843134109</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.02114604784160384</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.03313003466145011</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.9670390298034258</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>3.823869576491322</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>3.349075401492358</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>0.01059845365509916</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.04397412199349154</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.03997637458596782</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -993,13 +1012,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
